--- a/data/trans_camb/P1423-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1423-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,71</t>
+          <t>-0,59; 3,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,12</t>
+          <t>-1,89; 2,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,39</t>
+          <t>2,73; 8,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,7</t>
+          <t>4,91; 10,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,39</t>
+          <t>2,65; 8,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 11,15</t>
+          <t>5,36; 11,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,18</t>
+          <t>3,55; 7,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,37</t>
+          <t>1,08; 4,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,4</t>
+          <t>5,17; 9,34</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 86,41</t>
+          <t>-10,14; 88,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 47,45</t>
+          <t>-32,09; 60,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,22; 184,63</t>
+          <t>42,83; 194,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,35; 105,09</t>
+          <t>38,43; 106,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,2; 83,9</t>
+          <t>20,61; 84,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,6; 110,68</t>
+          <t>41,38; 112,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,15; 92,49</t>
+          <t>36,57; 90,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 68,44</t>
+          <t>11,16; 62,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,91; 120,05</t>
+          <t>53,92; 118,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,27</t>
+          <t>0,19; 2,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,02</t>
+          <t>0,09; 2,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,19</t>
+          <t>1,13; 4,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,41</t>
+          <t>0,21; 3,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,07</t>
+          <t>1,53; 4,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,26</t>
+          <t>1,31; 6,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,49</t>
+          <t>0,54; 2,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,19</t>
+          <t>1,07; 3,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,81</t>
+          <t>2,01; 4,89</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 161,02</t>
+          <t>7,65; 167,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 137,08</t>
+          <t>3,89; 147,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,73; 303,97</t>
+          <t>56,82; 285,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 71,26</t>
+          <t>2,48; 78,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,25; 107,28</t>
+          <t>23,18; 107,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,31; 133,73</t>
+          <t>24,18; 132,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 79,3</t>
+          <t>12,77; 79,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,23; 100,76</t>
+          <t>27,03; 98,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,8; 151,39</t>
+          <t>51,47; 151,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,41</t>
+          <t>-1,96; 2,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,1</t>
+          <t>-2,54; 1,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,79</t>
+          <t>0,26; 4,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,3</t>
+          <t>-3,01; 2,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,23</t>
+          <t>-3,53; 1,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,38</t>
+          <t>0,5; 5,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,73</t>
+          <t>-1,81; 1,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,58</t>
+          <t>-2,46; 0,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,49</t>
+          <t>1,21; 4,62</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,11; 142,74</t>
+          <t>-57,87; 111,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,61; 71,47</t>
+          <t>-70,19; 65,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,82; 262,61</t>
+          <t>0,7; 255,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,94; 76,34</t>
+          <t>-53,52; 84,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,34; 41,59</t>
+          <t>-62,86; 43,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 169,13</t>
+          <t>6,19; 193,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,14; 62,77</t>
+          <t>-44,66; 50,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,69; 21,34</t>
+          <t>-56,49; 22,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,56; 170,99</t>
+          <t>25,75; 170,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,97</t>
+          <t>0,18; 2,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,14</t>
+          <t>-0,62; 1,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,81</t>
+          <t>1,21; 3,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,15</t>
+          <t>2,34; 5,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,02</t>
+          <t>1,17; 3,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,15</t>
+          <t>1,48; 5,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,31</t>
+          <t>1,55; 3,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,27</t>
+          <t>0,54; 2,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,14</t>
+          <t>1,89; 4,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 74,37</t>
+          <t>4,91; 73,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 41,53</t>
+          <t>-17,56; 37,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,75; 141,01</t>
+          <t>37,81; 133,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,4; 74,06</t>
+          <t>28,79; 77,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,81; 57,91</t>
+          <t>14,28; 58,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,72; 73,73</t>
+          <t>18,89; 71,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,41; 66,86</t>
+          <t>27,56; 65,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,97; 44,49</t>
+          <t>8,56; 44,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,69; 83,1</t>
+          <t>33,7; 82,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1423-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1423-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>4,59</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,17</t>
+          <t>8,58</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>7,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,94</t>
+          <t>-0,43; 3,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,4</t>
+          <t>-2,05; 2,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,31</t>
+          <t>1,94; 7,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 10,68</t>
+          <t>5,0; 10,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,68</t>
+          <t>2,69; 8,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 11,05</t>
+          <t>5,8; 11,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,23</t>
+          <t>3,55; 7,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,98</t>
+          <t>1,36; 5,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,34</t>
+          <t>5,09; 9,28</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101,25%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 88,7</t>
+          <t>-8,24; 91,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 60,26</t>
+          <t>-32,11; 51,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,83; 194,37</t>
+          <t>30,28; 159,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,43; 106,37</t>
+          <t>38,54; 106,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,61; 84,2</t>
+          <t>21,53; 82,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,38; 112,76</t>
+          <t>45,62; 111,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,57; 90,71</t>
+          <t>36,57; 93,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 62,83</t>
+          <t>14,83; 68,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,92; 118,65</t>
+          <t>53,63; 118,57</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>4,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,33</t>
+          <t>0,2; 2,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,04</t>
+          <t>-0,03; 1,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,16</t>
+          <t>2,36; 4,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,64</t>
+          <t>0,21; 3,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,97</t>
+          <t>1,41; 5,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,24</t>
+          <t>3,91; 7,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,57</t>
+          <t>0,41; 2,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,07</t>
+          <t>1,12; 3,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,89</t>
+          <t>3,58; 5,53</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152,2%</t>
+          <t>185,44%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>124,05%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 167,91</t>
+          <t>5,15; 171,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 147,04</t>
+          <t>-2,4; 142,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,82; 285,57</t>
+          <t>88,69; 329,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 78,31</t>
+          <t>3,1; 78,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,18; 107,3</t>
+          <t>22,32; 107,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,18; 132,28</t>
+          <t>59,56; 154,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,77; 79,89</t>
+          <t>10,23; 75,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,03; 98,43</t>
+          <t>26,33; 97,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,47; 151,5</t>
+          <t>84,21; 173,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,37</t>
+          <t>-1,84; 2,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,05</t>
+          <t>-2,55; 1,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,97</t>
+          <t>0,54; 4,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,32</t>
+          <t>-3,39; 2,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,2</t>
+          <t>-3,81; 1,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,69</t>
+          <t>-0,03; 5,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,36</t>
+          <t>-1,71; 1,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,58</t>
+          <t>-2,45; 0,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,62</t>
+          <t>0,98; 4,46</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,87; 111,87</t>
+          <t>-56,91; 139,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 65,68</t>
+          <t>-71,4; 62,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 255,7</t>
+          <t>13,73; 262,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,52; 84,2</t>
+          <t>-58,8; 61,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,86; 43,28</t>
+          <t>-64,93; 49,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 193,7</t>
+          <t>-2,78; 178,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 50,25</t>
+          <t>-40,06; 59,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,49; 22,39</t>
+          <t>-56,79; 25,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,75; 170,51</t>
+          <t>18,8; 163,81</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,02</t>
+          <t>-0,01; 1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,01</t>
+          <t>-0,65; 1,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,68</t>
+          <t>2,03; 4,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,24</t>
+          <t>2,37; 5,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,98</t>
+          <t>1,16; 4,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,11</t>
+          <t>3,36; 5,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,27</t>
+          <t>1,54; 3,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,27</t>
+          <t>0,54; 2,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,22</t>
+          <t>3,09; 4,79</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,91; 73,99</t>
+          <t>-0,3; 71,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 37,34</t>
+          <t>-19,33; 41,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,81; 133,68</t>
+          <t>58,83; 155,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28,79; 77,22</t>
+          <t>29,03; 72,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,28; 58,93</t>
+          <t>14,72; 58,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,89; 71,98</t>
+          <t>41,01; 84,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,56; 65,51</t>
+          <t>26,54; 67,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,56; 44,52</t>
+          <t>10,14; 44,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,7; 82,79</t>
+          <t>53,84; 98,02</t>
         </is>
       </c>
     </row>
